--- a/Extra/TestScenarios.xlsx
+++ b/Extra/TestScenarios.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chouwzi\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914A14BB-392D-473D-9ED5-598B5AA7DAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" activeTab="8"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chức năng" sheetId="1" r:id="rId1"/>
@@ -49,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="130">
   <si>
     <t>No</t>
   </si>
@@ -444,14 +450,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -462,7 +462,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,146 +481,10 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -642,192 +505,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -850,255 +533,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1111,79 +555,31 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1199,13 +595,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1230,7 +632,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1246,13 +648,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 135804"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 135804">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1273,7 +681,7 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1289,13 +697,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 135804"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 135804">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1316,7 +730,7 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1332,13 +746,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 140745"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 140745">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1359,7 +779,7 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1375,13 +795,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1406,7 +832,7 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1422,13 +848,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1453,7 +885,7 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1469,13 +901,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1500,7 +938,7 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1516,13 +954,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1547,7 +991,7 @@
 </file>
 
 <file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1563,13 +1007,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1594,7 +1044,7 @@
 </file>
 
 <file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1610,13 +1060,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1641,7 +1097,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1659,13 +1115,18 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2" r:link="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" r:link="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1690,7 +1151,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1706,13 +1167,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 130915"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 130915">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1733,7 +1200,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1749,13 +1216,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 131110"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 131110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1776,7 +1249,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1792,13 +1265,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132005"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132005">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1819,7 +1298,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1835,13 +1314,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132222"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132222">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1862,7 +1347,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1878,13 +1363,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132611"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132611">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1905,7 +1396,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1921,13 +1412,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132705"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-04 132705">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1948,7 +1445,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1964,13 +1461,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2006,13 +1509,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2308,14 +1817,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2324,10 +1833,10 @@
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="52.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:10">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2359,7 +1868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:10">
+    <row r="2" spans="1:10" ht="30">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2378,20 +1887,16 @@
       <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:10">
+    <row r="3" spans="1:10" ht="30">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2410,20 +1915,16 @@
       <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:10">
+    <row r="4" spans="1:10" ht="30">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2442,20 +1943,16 @@
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="30">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2474,16 +1971,12 @@
       <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2506,16 +1999,12 @@
       <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2538,16 +2027,12 @@
       <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2570,20 +2055,16 @@
       <c r="F8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="30">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2602,16 +2083,12 @@
       <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="7" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2634,16 +2111,12 @@
       <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="7" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2666,16 +2139,12 @@
       <c r="F11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="7" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2698,20 +2167,16 @@
       <c r="F12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:10">
+    <row r="13" spans="1:10" ht="60">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2730,20 +2195,16 @@
       <c r="F13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="30">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2762,16 +2223,12 @@
       <c r="F14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2794,20 +2251,16 @@
       <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:10">
+    <row r="16" spans="1:10" ht="30">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2826,20 +2279,16 @@
       <c r="F16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" ht="30">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2858,20 +2307,16 @@
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:10">
+    <row r="18" spans="1:10" ht="30">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2890,20 +2335,16 @@
       <c r="F18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:10">
+    <row r="19" spans="1:10" ht="30">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2922,20 +2363,16 @@
       <c r="F19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
       <c r="I19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:10">
+    <row r="20" spans="1:10" ht="30">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2954,20 +2391,16 @@
       <c r="F20" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:10">
+    <row r="21" spans="1:10" ht="30">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2986,16 +2419,12 @@
       <c r="F21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
       <c r="I21" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3018,20 +2447,16 @@
       <c r="F22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
       <c r="I22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" ht="57.6" spans="1:10">
+    <row r="23" spans="1:10" ht="75">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3050,309 +2475,260 @@
       <c r="F23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="7" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" location="'test 1'!A1" display="test 1'!A1"/>
-    <hyperlink ref="J3" location="test2!A1" display="test2!A1"/>
-    <hyperlink ref="J4" location="'test 3'!A1" display="test 3'!A1"/>
-    <hyperlink ref="J5" location="'test 4'!A1" display="test 4'!A1"/>
-    <hyperlink ref="J6" location="'test 5'!A1" display="test 5'!A1"/>
-    <hyperlink ref="J7" location="'test 6'!A1" display="test 6'!A1"/>
-    <hyperlink ref="J8" location="'test 7'!A1" display="test 7'!A1"/>
-    <hyperlink ref="J9" location="'test 8'!A1" display="test 8'!A1"/>
-    <hyperlink ref="J10" location="'test 9'!A1" display="test 9'!A1"/>
-    <hyperlink ref="J11" location="'test 10'!A1" display="test 10'!A1"/>
-    <hyperlink ref="J12" location="'test 11'!A1" display="test 11'!A1"/>
-    <hyperlink ref="J14" location="'test 13'!A1" display="test 13'!A1"/>
-    <hyperlink ref="J15" location="'test 14'!A1" display="test 14'!A1"/>
-    <hyperlink ref="J16" location="'test 15'!A1" display="test 15'!A1"/>
-    <hyperlink ref="J17" location="'test 16'!A1" display="test 16'!A1"/>
-    <hyperlink ref="J13" location="'test 12'!A1" display="test 12'!A1"/>
-    <hyperlink ref="J18" location="'test 17'!A1" display="test 17'!A1"/>
-    <hyperlink ref="J19" location="'test 18'!A1" display="test 18'!A1"/>
-    <hyperlink ref="J20" location="'test 19'!A1" display="test 19'!A1"/>
-    <hyperlink ref="J21" location="'test 20'!A1" display="test 20'!A1"/>
-    <hyperlink ref="J22" location="'test 21'!A1" display="test 21'!A1"/>
-    <hyperlink ref="J23" location="'test 22'!A1" display="test 22'!A1"/>
+    <hyperlink ref="J2" location="'test 1'!A1" display="test 1'!A1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J3" location="test2!A1" display="test2!A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J4" location="'test 3'!A1" display="test 3'!A1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J5" location="'test 4'!A1" display="test 4'!A1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J6" location="'test 5'!A1" display="test 5'!A1" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J7" location="'test 6'!A1" display="test 6'!A1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J8" location="'test 7'!A1" display="test 7'!A1" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J9" location="'test 8'!A1" display="test 8'!A1" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J10" location="'test 9'!A1" display="test 9'!A1" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J11" location="'test 10'!A1" display="test 10'!A1" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J12" location="'test 11'!A1" display="test 11'!A1" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="J14" location="'test 13'!A1" display="test 13'!A1" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J15" location="'test 14'!A1" display="test 14'!A1" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="J16" location="'test 15'!A1" display="test 15'!A1" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="J17" location="'test 16'!A1" display="test 16'!A1" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="J13" location="'test 12'!A1" display="test 12'!A1" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="J18" location="'test 17'!A1" display="test 17'!A1" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="J19" location="'test 18'!A1" display="test 18'!A1" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="J20" location="'test 19'!A1" display="test 19'!A1" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="J21" location="'test 20'!A1" display="test 20'!A1" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="J22" location="'test 21'!A1" display="test 21'!A1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J23" location="'test 22'!A1" display="test 22'!A1" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>